--- a/.cache/products_catalog.xlsx
+++ b/.cache/products_catalog.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
+    <sheet name="Hampers" r:id="rId2" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>Better for you Options</t>
   </si>
@@ -297,6 +298,156 @@
   </si>
   <si>
     <t>Maaza</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>breadth</t>
+  </si>
+  <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>LED tealight candle</t>
+  </si>
+  <si>
+    <t>Besan Laddoo Cookies 100g</t>
+  </si>
+  <si>
+    <t>Inside item</t>
+  </si>
+  <si>
+    <t>Achari Aam Crackers 100g</t>
+  </si>
+  <si>
+    <t>Rava Laddoo Cookies 100g</t>
+  </si>
+  <si>
+    <t>Cheesy Chand Crunch 70g</t>
+  </si>
+  <si>
+    <t>Baked Mathri 75g</t>
+  </si>
+  <si>
+    <t>Pack of 2 (3x1x1.7 inch) chocolate</t>
+  </si>
+  <si>
+    <t>Chocolate (pack of 4)</t>
+  </si>
+  <si>
+    <t>Ajwain Cookies</t>
+  </si>
+  <si>
+    <t>Truffle (pack of 9)</t>
+  </si>
+  <si>
+    <t>Cinnamon hot chocolate</t>
+  </si>
+  <si>
+    <t>Chocolate (2) + tea light candle (2)</t>
+  </si>
+  <si>
+    <t>soy wax tea light (2)</t>
+  </si>
+  <si>
+    <t>Farmley mixed nuts 21g</t>
+  </si>
+  <si>
+    <t>Tealight candle (pack of 2)</t>
+  </si>
+  <si>
+    <t>Elephants tea light holder</t>
+  </si>
+  <si>
+    <t>Tote Bag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDF Tray 10x6 - 270/- </t>
+  </si>
+  <si>
+    <t>Hamper box</t>
+  </si>
+  <si>
+    <t>Small lamp</t>
+  </si>
+  <si>
+    <t>Craft Lantern</t>
+  </si>
+  <si>
+    <t>Tealight pack of 4</t>
+  </si>
+  <si>
+    <t>11 x 4.5 x 2.5 inch box - bougenvilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5 x 7 x 3.5 inch box - blue </t>
+  </si>
+  <si>
+    <t>10 x 10 x 3 w cavity - Jaipur palace</t>
+  </si>
+  <si>
+    <t>10 x 10 x 3 w/o cavity - Jaipur palace</t>
+  </si>
+  <si>
+    <t>10 x 10 x 3 - 9 inch</t>
+  </si>
+  <si>
+    <t>Greeting Card</t>
+  </si>
+  <si>
+    <t>Lotus Bowl</t>
+  </si>
+  <si>
+    <t>Chocolate Bar</t>
+  </si>
+  <si>
+    <t>Dry fruit 200g tin - almond</t>
+  </si>
+  <si>
+    <t>Brass Lamp</t>
+  </si>
+  <si>
+    <t>Phool incense cone</t>
+  </si>
+  <si>
+    <t>Dry fruit 200g tin - cashew</t>
+  </si>
+  <si>
+    <t>Dry fruit 200g tin - raisin</t>
+  </si>
+  <si>
+    <t>Dry fruit 150g tin - nutty mix</t>
+  </si>
+  <si>
+    <t>Dry fruit 150g tin - almond</t>
+  </si>
+  <si>
+    <t>Dry fruit 200g tin - nutty mix</t>
+  </si>
+  <si>
+    <t>Dry fruit 100g tin - nutty mix</t>
+  </si>
+  <si>
+    <t>Besan small tin</t>
+  </si>
+  <si>
+    <t>Gingerbread cookies</t>
+  </si>
+  <si>
+    <t>Guntur Piri Piri</t>
+  </si>
+  <si>
+    <t>Besan hexagon</t>
+  </si>
+  <si>
+    <t>Rava Hexagon</t>
+  </si>
+  <si>
+    <t>Achari Hexagon</t>
   </si>
 </sst>
 </file>
@@ -309,29 +460,34 @@
   <fonts count="6">
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <color theme="1"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Roboto"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Roboto"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Roboto"/>
     </font>
   </fonts>
@@ -415,60 +571,63 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0">
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="0" numFmtId="164" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="0" numFmtId="164" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf borderId="3" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0">
+    <xf borderId="3" fillId="0" fontId="0" numFmtId="164" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0">
+    <xf borderId="4" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,6 +646,316 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="3C4F63"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="F4F6F6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="3498DB"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="2ECC71"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="F1C40F"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="E67622"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="EE4675"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="9B59B6"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="185C8A"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="3A62C8"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Roboto"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Roboto"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
   <dimension ref="A1:H83"/>
@@ -2788,4 +3257,320 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr defaultRowHeight="14.0" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="34.44"/>
+    <col min="2" max="2048" width="13.24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11">
+        <v>5.0</v>
+      </c>
+      <c r="D11">
+        <v>5.0</v>
+      </c>
+      <c r="E11">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18">
+        <v>3.0</v>
+      </c>
+      <c r="D18">
+        <v>3.0</v>
+      </c>
+      <c r="E18">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>